--- a/CE国試data/CE_questions_2021.xlsx
+++ b/CE国試data/CE_questions_2021.xlsx
@@ -3061,7 +3061,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
@@ -13209,7 +13209,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="T149" t="inlineStr">
